--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>3100</x:v>
+        <x:v>3931.6292160000003</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>2.3</x:v>
+        <x:v>3.3511119999999996</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>69.5</x:v>
+        <x:v>73.2</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>3931.6292160000003</x:v>
+        <x:v>3935</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>3.3511119999999996</x:v>
+        <x:v>3.34</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>73.2</x:v>
+        <x:v>72.9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>3935</x:v>
+        <x:v>3932</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>3.34</x:v>
+        <x:v>3.355</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>72.9</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>3932</x:v>
+        <x:v>3930</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>3.355</x:v>
+        <x:v>3.35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>73</x:v>
+        <x:v>73.1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>3930</x:v>
+        <x:v>3958</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>3.35</x:v>
+        <x:v>3.4</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
